--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="300">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -880,6 +880,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -3673,7 +3676,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4088,153 +4091,174 @@
         <v>273</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" s="67">
+        <v>284</v>
+      </c>
+      <c r="D23" s="67">
+        <v>771</v>
+      </c>
+      <c r="E23" s="67">
+        <v>1545</v>
+      </c>
+      <c r="F23" s="67">
+        <v>2477</v>
+      </c>
+      <c r="G23" s="67">
+        <v>3502</v>
+      </c>
+      <c r="H23" s="65" t="s">
         <v>274</v>
       </c>
-      <c r="C24" s="5" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="72" t="s">
+      <c r="E25" s="5"/>
+      <c r="F25" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="C25" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="D25" s="73" t="s">
-        <v>280</v>
-      </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74" t="s">
-        <v>281</v>
-      </c>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="72" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D26" s="73" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E26" s="73"/>
       <c r="F26" s="74" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G26" s="74"/>
       <c r="H26" s="74"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="72" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D27" s="73" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E27" s="73"/>
       <c r="F27" s="74" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G27" s="74"/>
       <c r="H27" s="74"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="72" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D28" s="73" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E28" s="73"/>
       <c r="F28" s="74" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G28" s="74"/>
       <c r="H28" s="74"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="72" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D29" s="73" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E29" s="73"/>
       <c r="F29" s="74" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G29" s="74"/>
       <c r="H29" s="74"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="72" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D30" s="73" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E30" s="73"/>
       <c r="F30" s="74" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G30" s="74"/>
       <c r="H30" s="74"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="72" t="s">
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="72" t="s">
+        <v>295</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="D31" s="73" t="s">
+        <v>296</v>
+      </c>
+      <c r="E31" s="73"/>
+      <c r="F31" s="74" t="s">
+        <v>297</v>
+      </c>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="72" t="s">
         <v>249</v>
       </c>
-      <c r="C32" s="61" t="s">
-        <v>297</v>
-      </c>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="75" t="s">
+      <c r="C33" s="61" t="s">
         <v>298</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="75" t="s">
+        <v>299</v>
+      </c>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -4247,8 +4271,10 @@
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="304">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -844,6 +844,18 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1224,7 +1236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1315,6 +1327,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3676,7 +3694,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3925,356 +3943,439 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="66">
+        <v>6276.066666666667</v>
+      </c>
+      <c r="D16" s="66">
+        <v>5497.863636363636</v>
+      </c>
+      <c r="E16" s="66">
+        <v>4331.633333333333</v>
+      </c>
+      <c r="F16" s="66">
+        <v>3831.1944444444443</v>
+      </c>
+      <c r="G16" s="66">
+        <v>3619.55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="C16" s="63">
-        <v>0.38517014925373133</v>
-      </c>
-      <c r="D16" s="63">
-        <v>0.2631922899201267</v>
-      </c>
-      <c r="E16" s="63">
-        <v>0.19337932333482447</v>
-      </c>
-      <c r="F16" s="63">
-        <v>0.16157607242446237</v>
-      </c>
-      <c r="G16" s="63">
-        <v>0.1456539181599358</v>
-      </c>
-      <c r="H16" s="65" t="s">
+      <c r="C17" s="60">
+        <v>0</v>
+      </c>
+      <c r="D17" s="60">
+        <v>0</v>
+      </c>
+      <c r="E17" s="60">
+        <v>0</v>
+      </c>
+      <c r="F17" s="60">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="61" t="s">
+      <c r="C18" s="64">
+        <v>1720</v>
+      </c>
+      <c r="D18" s="64">
+        <v>1206.9545454545455</v>
+      </c>
+      <c r="E18" s="64">
+        <v>910.9354999999999</v>
+      </c>
+      <c r="F18" s="64">
+        <v>781.2734395833334</v>
+      </c>
+      <c r="G18" s="64">
+        <v>723.675110915625</v>
+      </c>
+      <c r="H18" s="65" t="s">
         <v>264</v>
       </c>
-      <c r="C17" s="66">
-        <v>0.15402985074626865</v>
-      </c>
-      <c r="D17" s="63">
-        <v>0.08763944814839263</v>
-      </c>
-      <c r="E17" s="63">
-        <v>0.06434220563652203</v>
-      </c>
-      <c r="F17" s="63">
-        <v>0.05371833115283242</v>
-      </c>
-      <c r="G17" s="63">
-        <v>0.04838694242548977</v>
-      </c>
-      <c r="H17" s="65" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="61" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="61" t="s">
-        <v>266</v>
-      </c>
-      <c r="C18" s="63">
-        <v>0.4379641791044776</v>
-      </c>
-      <c r="D18" s="63">
-        <v>0.600788830945937</v>
-      </c>
-      <c r="E18" s="63">
-        <v>0.6940432745508912</v>
-      </c>
-      <c r="F18" s="63">
-        <v>0.7365770273883647</v>
-      </c>
-      <c r="G18" s="63">
-        <v>0.7579867611660872</v>
-      </c>
-      <c r="H18" s="65" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="61" t="s">
-        <v>268</v>
-      </c>
       <c r="C19" s="67">
-        <v>3</v>
+        <v>4890.6</v>
       </c>
       <c r="D19" s="67">
-        <v>3</v>
+        <v>8273.954545454546</v>
       </c>
       <c r="E19" s="67">
-        <v>3</v>
+        <v>9826</v>
       </c>
       <c r="F19" s="67">
-        <v>3</v>
+        <v>10712.694444444445</v>
       </c>
       <c r="G19" s="67">
-        <v>3</v>
-      </c>
-      <c r="H19" s="65" t="s">
-        <v>269</v>
+        <v>11336.45</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="61" t="s">
-        <v>177</v>
-      </c>
-      <c r="C20" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="E20" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="F20" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="G20" s="68" t="s">
-        <v>178</v>
+        <v>266</v>
+      </c>
+      <c r="C20" s="63">
+        <v>0.38517014925373133</v>
+      </c>
+      <c r="D20" s="63">
+        <v>0.2631922899201267</v>
+      </c>
+      <c r="E20" s="63">
+        <v>0.19337932333482447</v>
+      </c>
+      <c r="F20" s="63">
+        <v>0.16157607242446237</v>
+      </c>
+      <c r="G20" s="63">
+        <v>0.1456539181599358</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>178</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="61" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="68">
+        <v>0.15402985074626865</v>
+      </c>
+      <c r="D21" s="63">
+        <v>0.08763944814839263</v>
+      </c>
+      <c r="E21" s="63">
+        <v>0.06434220563652203</v>
+      </c>
+      <c r="F21" s="63">
+        <v>0.05371833115283242</v>
+      </c>
+      <c r="G21" s="63">
+        <v>0.04838694242548977</v>
+      </c>
+      <c r="H21" s="65" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="61" t="s">
         <v>270</v>
       </c>
-      <c r="C21" s="29" t="str">
+      <c r="C22" s="63">
+        <v>0.4379641791044776</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.600788830945937</v>
+      </c>
+      <c r="E22" s="63">
+        <v>0.6940432745508912</v>
+      </c>
+      <c r="F22" s="63">
+        <v>0.7365770273883647</v>
+      </c>
+      <c r="G22" s="63">
+        <v>0.7579867611660872</v>
+      </c>
+      <c r="H22" s="65" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" s="69">
+        <v>3</v>
+      </c>
+      <c r="D23" s="69">
+        <v>3</v>
+      </c>
+      <c r="E23" s="69">
+        <v>3</v>
+      </c>
+      <c r="F23" s="69">
+        <v>3</v>
+      </c>
+      <c r="G23" s="69">
+        <v>3</v>
+      </c>
+      <c r="H23" s="65" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="C24" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="D24" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="F24" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="G24" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="65" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" s="29" t="str">
         <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="69" t="str">
+      <c r="D25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="69" t="str">
+      <c r="E25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="69" t="str">
+      <c r="F25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="69" t="str">
+      <c r="G25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H25" s="65" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="61" t="s">
-        <v>271</v>
-      </c>
-      <c r="C22" s="70">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26" s="72">
         <v>9</v>
       </c>
-      <c r="D22" s="67">
+      <c r="D26" s="69">
         <v>25</v>
       </c>
-      <c r="E22" s="67">
+      <c r="E26" s="69">
         <v>51</v>
       </c>
-      <c r="F22" s="71" t="s">
-        <v>272</v>
-      </c>
-      <c r="G22" s="71" t="s">
-        <v>272</v>
-      </c>
-      <c r="H22" s="65" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="61" t="s">
+      <c r="F26" s="73" t="s">
+        <v>276</v>
+      </c>
+      <c r="G26" s="73" t="s">
+        <v>276</v>
+      </c>
+      <c r="H26" s="65" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="C23" s="67">
+      <c r="C27" s="69">
         <v>284</v>
       </c>
-      <c r="D23" s="67">
+      <c r="D27" s="69">
         <v>771</v>
       </c>
-      <c r="E23" s="67">
+      <c r="E27" s="69">
         <v>1545</v>
       </c>
-      <c r="F23" s="67">
+      <c r="F27" s="69">
         <v>2477</v>
       </c>
-      <c r="G23" s="67">
+      <c r="G27" s="69">
         <v>3502</v>
       </c>
-      <c r="H23" s="65" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5" t="s">
+      <c r="H27" s="65" t="s">
         <v>278</v>
       </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="72" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C29" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="D26" s="73" t="s">
+      <c r="D29" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74" t="s">
+      <c r="E29" s="5"/>
+      <c r="F29" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="72" t="s">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="74" t="s">
         <v>283</v>
       </c>
-      <c r="C27" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="D27" s="73" t="s">
+      <c r="C30" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74" t="s">
+      <c r="D30" s="75" t="s">
         <v>285</v>
       </c>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="72" t="s">
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
         <v>286</v>
       </c>
-      <c r="C28" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="D28" s="73" t="s">
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="74" t="s">
         <v>287</v>
       </c>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74" t="s">
+      <c r="C31" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D31" s="75" t="s">
         <v>288</v>
       </c>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="72" t="s">
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
         <v>289</v>
       </c>
-      <c r="C29" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="D29" s="73" t="s">
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="74" t="s">
         <v>290</v>
       </c>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74" t="s">
+      <c r="C32" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" s="75" t="s">
         <v>291</v>
       </c>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="72" t="s">
+      <c r="E32" s="75"/>
+      <c r="F32" s="76" t="s">
         <v>292</v>
       </c>
-      <c r="C30" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="D30" s="73" t="s">
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="74" t="s">
         <v>293</v>
       </c>
-      <c r="E30" s="73"/>
-      <c r="F30" s="74" t="s">
+      <c r="C33" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D33" s="75" t="s">
         <v>294</v>
       </c>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="72" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="76" t="s">
         <v>295</v>
       </c>
-      <c r="C31" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="D31" s="73" t="s">
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="74" t="s">
         <v>296</v>
       </c>
-      <c r="E31" s="73"/>
-      <c r="F31" s="74" t="s">
+      <c r="C34" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D34" s="75" t="s">
         <v>297</v>
       </c>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="72" t="s">
+      <c r="E34" s="75"/>
+      <c r="F34" s="76" t="s">
+        <v>298</v>
+      </c>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="74" t="s">
+        <v>299</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D35" s="75" t="s">
+        <v>300</v>
+      </c>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76" t="s">
+        <v>301</v>
+      </c>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="74" t="s">
         <v>249</v>
       </c>
-      <c r="C33" s="61" t="s">
-        <v>298</v>
-      </c>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="75" t="s">
-        <v>299</v>
-      </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
+      <c r="C37" s="61" t="s">
+        <v>302</v>
+      </c>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="77" t="s">
+        <v>303</v>
+      </c>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4320,37 +4421,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="299">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -846,18 +846,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -892,9 +880,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1236,7 +1221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1327,12 +1312,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3694,7 +3673,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3943,439 +3922,333 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="66">
-        <v>6276.066666666667</v>
-      </c>
-      <c r="D16" s="66">
-        <v>5497.863636363636</v>
-      </c>
-      <c r="E16" s="66">
-        <v>4331.633333333333</v>
-      </c>
-      <c r="F16" s="66">
-        <v>3831.1944444444443</v>
-      </c>
-      <c r="G16" s="66">
-        <v>3619.55</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="C17" s="60">
-        <v>0</v>
-      </c>
-      <c r="D17" s="60">
-        <v>0</v>
-      </c>
-      <c r="E17" s="60">
-        <v>0</v>
-      </c>
-      <c r="F17" s="60">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60">
-        <v>0</v>
+      <c r="C16" s="63">
+        <v>0.38517014925373133</v>
+      </c>
+      <c r="D16" s="63">
+        <v>0.2631922899201267</v>
+      </c>
+      <c r="E16" s="63">
+        <v>0.19337932333482447</v>
+      </c>
+      <c r="F16" s="63">
+        <v>0.16157607242446237</v>
+      </c>
+      <c r="G16" s="63">
+        <v>0.1456539181599358</v>
+      </c>
+      <c r="H16" s="65" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="C17" s="66">
+        <v>0.15402985074626865</v>
+      </c>
+      <c r="D17" s="63">
+        <v>0.08763944814839263</v>
+      </c>
+      <c r="E17" s="63">
+        <v>0.06434220563652203</v>
+      </c>
+      <c r="F17" s="63">
+        <v>0.05371833115283242</v>
+      </c>
+      <c r="G17" s="63">
+        <v>0.04838694242548977</v>
+      </c>
+      <c r="H17" s="65" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="C18" s="64">
-        <v>1720</v>
-      </c>
-      <c r="D18" s="64">
-        <v>1206.9545454545455</v>
-      </c>
-      <c r="E18" s="64">
-        <v>910.9354999999999</v>
-      </c>
-      <c r="F18" s="64">
-        <v>781.2734395833334</v>
-      </c>
-      <c r="G18" s="64">
-        <v>723.675110915625</v>
+      <c r="B18" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="C18" s="63">
+        <v>0.4379641791044776</v>
+      </c>
+      <c r="D18" s="63">
+        <v>0.600788830945937</v>
+      </c>
+      <c r="E18" s="63">
+        <v>0.6940432745508912</v>
+      </c>
+      <c r="F18" s="63">
+        <v>0.7365770273883647</v>
+      </c>
+      <c r="G18" s="63">
+        <v>0.7579867611660872</v>
       </c>
       <c r="H18" s="65" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="61" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C19" s="67">
-        <v>4890.6</v>
+        <v>3</v>
       </c>
       <c r="D19" s="67">
-        <v>8273.954545454546</v>
+        <v>3</v>
       </c>
       <c r="E19" s="67">
-        <v>9826</v>
+        <v>3</v>
       </c>
       <c r="F19" s="67">
-        <v>10712.694444444445</v>
+        <v>3</v>
       </c>
       <c r="G19" s="67">
-        <v>11336.45</v>
+        <v>3</v>
+      </c>
+      <c r="H19" s="65" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="61" t="s">
-        <v>266</v>
-      </c>
-      <c r="C20" s="63">
-        <v>0.38517014925373133</v>
-      </c>
-      <c r="D20" s="63">
-        <v>0.2631922899201267</v>
-      </c>
-      <c r="E20" s="63">
-        <v>0.19337932333482447</v>
-      </c>
-      <c r="F20" s="63">
-        <v>0.16157607242446237</v>
-      </c>
-      <c r="G20" s="63">
-        <v>0.1456539181599358</v>
+        <v>177</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G20" s="68" t="s">
+        <v>178</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>267</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="61" t="s">
-        <v>268</v>
-      </c>
-      <c r="C21" s="68">
-        <v>0.15402985074626865</v>
-      </c>
-      <c r="D21" s="63">
-        <v>0.08763944814839263</v>
-      </c>
-      <c r="E21" s="63">
-        <v>0.06434220563652203</v>
-      </c>
-      <c r="F21" s="63">
-        <v>0.05371833115283242</v>
-      </c>
-      <c r="G21" s="63">
-        <v>0.04838694242548977</v>
+        <v>270</v>
+      </c>
+      <c r="C21" s="29" t="str">
+        <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="69" t="str">
+        <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="69" t="str">
+        <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="69" t="str">
+        <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="69" t="str">
+        <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>269</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="61" t="s">
-        <v>270</v>
-      </c>
-      <c r="C22" s="63">
-        <v>0.4379641791044776</v>
-      </c>
-      <c r="D22" s="63">
-        <v>0.600788830945937</v>
-      </c>
-      <c r="E22" s="63">
-        <v>0.6940432745508912</v>
-      </c>
-      <c r="F22" s="63">
-        <v>0.7365770273883647</v>
-      </c>
-      <c r="G22" s="63">
-        <v>0.7579867611660872</v>
+        <v>271</v>
+      </c>
+      <c r="C22" s="70">
+        <v>9</v>
+      </c>
+      <c r="D22" s="67">
+        <v>25</v>
+      </c>
+      <c r="E22" s="67">
+        <v>51</v>
+      </c>
+      <c r="F22" s="71" t="s">
+        <v>272</v>
+      </c>
+      <c r="G22" s="71" t="s">
+        <v>272</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="61" t="s">
-        <v>272</v>
-      </c>
-      <c r="C23" s="69">
-        <v>3</v>
-      </c>
-      <c r="D23" s="69">
-        <v>3</v>
-      </c>
-      <c r="E23" s="69">
-        <v>3</v>
-      </c>
-      <c r="F23" s="69">
-        <v>3</v>
-      </c>
-      <c r="G23" s="69">
-        <v>3</v>
-      </c>
-      <c r="H23" s="65" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="61" t="s">
-        <v>177</v>
-      </c>
-      <c r="C24" s="70" t="s">
-        <v>178</v>
-      </c>
-      <c r="D24" s="70" t="s">
-        <v>178</v>
-      </c>
-      <c r="E24" s="70" t="s">
-        <v>178</v>
-      </c>
-      <c r="F24" s="70" t="s">
-        <v>178</v>
-      </c>
-      <c r="G24" s="70" t="s">
-        <v>178</v>
-      </c>
-      <c r="H24" s="65" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="61" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C25" s="29" t="str">
-        <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="D25" s="71" t="str">
-        <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="71" t="str">
-        <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="71" t="str">
-        <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="71" t="str">
-        <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="65" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="61" t="s">
+      <c r="C24" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C26" s="72">
-        <v>9</v>
-      </c>
-      <c r="D26" s="69">
-        <v>25</v>
-      </c>
-      <c r="E26" s="69">
-        <v>51</v>
-      </c>
-      <c r="F26" s="73" t="s">
+      <c r="D24" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="G26" s="73" t="s">
-        <v>276</v>
-      </c>
-      <c r="H26" s="65" t="s">
+      <c r="E24" s="5"/>
+      <c r="F24" s="5" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="C27" s="69">
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="72" t="s">
+        <v>278</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="D25" s="73" t="s">
+        <v>280</v>
+      </c>
+      <c r="E25" s="73"/>
+      <c r="F25" s="74" t="s">
+        <v>281</v>
+      </c>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="72" t="s">
+        <v>282</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="D26" s="73" t="s">
+        <v>283</v>
+      </c>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74" t="s">
         <v>284</v>
       </c>
-      <c r="D27" s="69">
-        <v>771</v>
-      </c>
-      <c r="E27" s="69">
-        <v>1545</v>
-      </c>
-      <c r="F27" s="69">
-        <v>2477</v>
-      </c>
-      <c r="G27" s="69">
-        <v>3502</v>
-      </c>
-      <c r="H27" s="65" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="C27" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="D27" s="73" t="s">
+        <v>286</v>
+      </c>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74" t="s">
+        <v>287</v>
+      </c>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="72" t="s">
+        <v>288</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="D28" s="73" t="s">
+        <v>289</v>
+      </c>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74" t="s">
+        <v>290</v>
+      </c>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="72" t="s">
+        <v>291</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="D29" s="73" t="s">
+        <v>292</v>
+      </c>
+      <c r="E29" s="73"/>
+      <c r="F29" s="74" t="s">
+        <v>293</v>
+      </c>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="74" t="s">
-        <v>283</v>
+      <c r="B30" s="72" t="s">
+        <v>294</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>285</v>
-      </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
-        <v>286</v>
-      </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="74" t="s">
-        <v>287</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="D31" s="75" t="s">
-        <v>288</v>
-      </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
-        <v>289</v>
-      </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="74" t="s">
-        <v>290</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="D32" s="75" t="s">
-        <v>291</v>
-      </c>
-      <c r="E32" s="75"/>
-      <c r="F32" s="76" t="s">
-        <v>292</v>
-      </c>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="74" t="s">
-        <v>293</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="D33" s="75" t="s">
-        <v>294</v>
-      </c>
-      <c r="E33" s="75"/>
-      <c r="F33" s="76" t="s">
+        <v>279</v>
+      </c>
+      <c r="D30" s="73" t="s">
         <v>295</v>
       </c>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="74" t="s">
+      <c r="E30" s="73"/>
+      <c r="F30" s="74" t="s">
         <v>296</v>
       </c>
-      <c r="C34" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="D34" s="75" t="s">
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="72" t="s">
+        <v>249</v>
+      </c>
+      <c r="C32" s="61" t="s">
         <v>297</v>
       </c>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="75" t="s">
+        <v>298</v>
+      </c>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
       <c r="E34" s="75"/>
-      <c r="F34" s="76" t="s">
-        <v>298</v>
-      </c>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="74" t="s">
-        <v>299</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="D35" s="75" t="s">
-        <v>300</v>
-      </c>
-      <c r="E35" s="75"/>
-      <c r="F35" s="76" t="s">
-        <v>301</v>
-      </c>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="74" t="s">
-        <v>249</v>
-      </c>
-      <c r="C37" s="61" t="s">
-        <v>302</v>
-      </c>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="77" t="s">
-        <v>303</v>
-      </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="B34:H34"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4421,37 +4294,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="304">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -846,6 +846,18 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -880,6 +892,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1221,7 +1236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1312,6 +1327,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3673,7 +3694,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3922,333 +3943,439 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="66">
+        <v>6276.066666666667</v>
+      </c>
+      <c r="D16" s="66">
+        <v>5497.863636363636</v>
+      </c>
+      <c r="E16" s="66">
+        <v>4331.633333333333</v>
+      </c>
+      <c r="F16" s="66">
+        <v>3831.1944444444443</v>
+      </c>
+      <c r="G16" s="66">
+        <v>3619.55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="C16" s="63">
-        <v>0.38517014925373133</v>
-      </c>
-      <c r="D16" s="63">
-        <v>0.2631922899201267</v>
-      </c>
-      <c r="E16" s="63">
-        <v>0.19337932333482447</v>
-      </c>
-      <c r="F16" s="63">
-        <v>0.16157607242446237</v>
-      </c>
-      <c r="G16" s="63">
-        <v>0.1456539181599358</v>
-      </c>
-      <c r="H16" s="65" t="s">
+      <c r="C17" s="60">
+        <v>0</v>
+      </c>
+      <c r="D17" s="60">
+        <v>0</v>
+      </c>
+      <c r="E17" s="60">
+        <v>0</v>
+      </c>
+      <c r="F17" s="60">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="61" t="s">
+      <c r="C18" s="64">
+        <v>1720</v>
+      </c>
+      <c r="D18" s="64">
+        <v>1206.9545454545455</v>
+      </c>
+      <c r="E18" s="64">
+        <v>910.9354999999999</v>
+      </c>
+      <c r="F18" s="64">
+        <v>781.2734395833334</v>
+      </c>
+      <c r="G18" s="64">
+        <v>723.675110915625</v>
+      </c>
+      <c r="H18" s="65" t="s">
         <v>264</v>
       </c>
-      <c r="C17" s="66">
-        <v>0.15402985074626865</v>
-      </c>
-      <c r="D17" s="63">
-        <v>0.08763944814839263</v>
-      </c>
-      <c r="E17" s="63">
-        <v>0.06434220563652203</v>
-      </c>
-      <c r="F17" s="63">
-        <v>0.05371833115283242</v>
-      </c>
-      <c r="G17" s="63">
-        <v>0.04838694242548977</v>
-      </c>
-      <c r="H17" s="65" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="61" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="61" t="s">
-        <v>266</v>
-      </c>
-      <c r="C18" s="63">
-        <v>0.4379641791044776</v>
-      </c>
-      <c r="D18" s="63">
-        <v>0.600788830945937</v>
-      </c>
-      <c r="E18" s="63">
-        <v>0.6940432745508912</v>
-      </c>
-      <c r="F18" s="63">
-        <v>0.7365770273883647</v>
-      </c>
-      <c r="G18" s="63">
-        <v>0.7579867611660872</v>
-      </c>
-      <c r="H18" s="65" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="61" t="s">
-        <v>268</v>
-      </c>
       <c r="C19" s="67">
-        <v>3</v>
+        <v>4890.6</v>
       </c>
       <c r="D19" s="67">
-        <v>3</v>
+        <v>8273.954545454546</v>
       </c>
       <c r="E19" s="67">
-        <v>3</v>
+        <v>9826</v>
       </c>
       <c r="F19" s="67">
-        <v>3</v>
+        <v>10712.694444444445</v>
       </c>
       <c r="G19" s="67">
-        <v>3</v>
-      </c>
-      <c r="H19" s="65" t="s">
-        <v>269</v>
+        <v>11336.45</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="61" t="s">
-        <v>177</v>
-      </c>
-      <c r="C20" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="E20" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="F20" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="G20" s="68" t="s">
-        <v>178</v>
+        <v>266</v>
+      </c>
+      <c r="C20" s="63">
+        <v>0.38517014925373133</v>
+      </c>
+      <c r="D20" s="63">
+        <v>0.2631922899201267</v>
+      </c>
+      <c r="E20" s="63">
+        <v>0.19337932333482447</v>
+      </c>
+      <c r="F20" s="63">
+        <v>0.16157607242446237</v>
+      </c>
+      <c r="G20" s="63">
+        <v>0.1456539181599358</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>178</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="61" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="68">
+        <v>0.15402985074626865</v>
+      </c>
+      <c r="D21" s="63">
+        <v>0.08763944814839263</v>
+      </c>
+      <c r="E21" s="63">
+        <v>0.06434220563652203</v>
+      </c>
+      <c r="F21" s="63">
+        <v>0.05371833115283242</v>
+      </c>
+      <c r="G21" s="63">
+        <v>0.04838694242548977</v>
+      </c>
+      <c r="H21" s="65" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="61" t="s">
         <v>270</v>
       </c>
-      <c r="C21" s="29" t="str">
+      <c r="C22" s="63">
+        <v>0.4379641791044776</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.600788830945937</v>
+      </c>
+      <c r="E22" s="63">
+        <v>0.6940432745508912</v>
+      </c>
+      <c r="F22" s="63">
+        <v>0.7365770273883647</v>
+      </c>
+      <c r="G22" s="63">
+        <v>0.7579867611660872</v>
+      </c>
+      <c r="H22" s="65" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" s="69">
+        <v>3</v>
+      </c>
+      <c r="D23" s="69">
+        <v>3</v>
+      </c>
+      <c r="E23" s="69">
+        <v>3</v>
+      </c>
+      <c r="F23" s="69">
+        <v>3</v>
+      </c>
+      <c r="G23" s="69">
+        <v>3</v>
+      </c>
+      <c r="H23" s="65" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="C24" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="D24" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="F24" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="G24" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="65" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" s="29" t="str">
         <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="69" t="str">
+      <c r="D25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="69" t="str">
+      <c r="E25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="69" t="str">
+      <c r="F25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="69" t="str">
+      <c r="G25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H25" s="65" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="61" t="s">
-        <v>271</v>
-      </c>
-      <c r="C22" s="70">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26" s="72">
         <v>9</v>
       </c>
-      <c r="D22" s="67">
+      <c r="D26" s="69">
         <v>25</v>
       </c>
-      <c r="E22" s="67">
+      <c r="E26" s="69">
         <v>51</v>
       </c>
-      <c r="F22" s="71" t="s">
-        <v>272</v>
-      </c>
-      <c r="G22" s="71" t="s">
-        <v>272</v>
-      </c>
-      <c r="H22" s="65" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="F26" s="73" t="s">
         <v>276</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5" t="s">
+      <c r="G26" s="73" t="s">
+        <v>276</v>
+      </c>
+      <c r="H26" s="65" t="s">
         <v>277</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="72" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="69">
+        <v>284</v>
+      </c>
+      <c r="D27" s="69">
+        <v>771</v>
+      </c>
+      <c r="E27" s="69">
+        <v>1545</v>
+      </c>
+      <c r="F27" s="69">
+        <v>2477</v>
+      </c>
+      <c r="G27" s="69">
+        <v>3502</v>
+      </c>
+      <c r="H27" s="65" t="s">
         <v>278</v>
       </c>
-      <c r="C25" s="29" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="C29" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74" t="s">
+      <c r="D29" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="72" t="s">
+      <c r="E29" s="5"/>
+      <c r="F29" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="C26" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="D26" s="73" t="s">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="74" t="s">
         <v>283</v>
       </c>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74" t="s">
+      <c r="C30" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="72" t="s">
+      <c r="D30" s="75" t="s">
         <v>285</v>
       </c>
-      <c r="C27" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="D27" s="73" t="s">
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
         <v>286</v>
       </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74" t="s">
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="74" t="s">
         <v>287</v>
       </c>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="72" t="s">
+      <c r="C31" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D31" s="75" t="s">
         <v>288</v>
       </c>
-      <c r="C28" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="D28" s="73" t="s">
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
         <v>289</v>
       </c>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74" t="s">
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="74" t="s">
         <v>290</v>
       </c>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="72" t="s">
+      <c r="C32" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" s="75" t="s">
         <v>291</v>
       </c>
-      <c r="C29" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="D29" s="73" t="s">
+      <c r="E32" s="75"/>
+      <c r="F32" s="76" t="s">
         <v>292</v>
       </c>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74" t="s">
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="74" t="s">
         <v>293</v>
       </c>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="72" t="s">
+      <c r="C33" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D33" s="75" t="s">
         <v>294</v>
       </c>
-      <c r="C30" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="D30" s="73" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="76" t="s">
         <v>295</v>
       </c>
-      <c r="E30" s="73"/>
-      <c r="F30" s="74" t="s">
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="74" t="s">
         <v>296</v>
       </c>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="72" t="s">
+      <c r="C34" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D34" s="75" t="s">
+        <v>297</v>
+      </c>
+      <c r="E34" s="75"/>
+      <c r="F34" s="76" t="s">
+        <v>298</v>
+      </c>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="74" t="s">
+        <v>299</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D35" s="75" t="s">
+        <v>300</v>
+      </c>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76" t="s">
+        <v>301</v>
+      </c>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="74" t="s">
         <v>249</v>
       </c>
-      <c r="C32" s="61" t="s">
-        <v>297</v>
-      </c>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="75" t="s">
-        <v>298</v>
-      </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
+      <c r="C37" s="61" t="s">
+        <v>302</v>
+      </c>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="77" t="s">
+        <v>303</v>
+      </c>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4294,37 +4421,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tuition &amp; Funding Detail'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing Plan'!$A1:$H21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staffing Plan'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Operating Expenses'!$A1:$F11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Operating Expenses'!$A1:$F12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Facilities &amp; Occupancy'!$A1:$F9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Facilities &amp; Occupancy'!$1:$1</definedName>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="305">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -351,6 +351,9 @@
     <t>ADMINISTRATIVE / GENERAL</t>
   </si>
   <si>
+    <t>Compliance Contract</t>
+  </si>
+  <si>
     <t>Total Administrative / General</t>
   </si>
   <si>
@@ -615,7 +618,7 @@
     <t>COVENANT CHECKS</t>
   </si>
   <si>
-    <t>DSCR ≥ 1.20x</t>
+    <t>DSCR ≥ 1.25x</t>
   </si>
   <si>
     <t>Cash Reserve ≥ 2.0 Months</t>
@@ -645,7 +648,7 @@
     <t>Min 2 Months Cash Reserve (2026-27)</t>
   </si>
   <si>
-    <t>9.4 months</t>
+    <t>8.5 months</t>
   </si>
   <si>
     <t>Positive Net Income (2026-27)</t>
@@ -708,7 +711,7 @@
     <t>2026-27 Cash Reserve (Months)</t>
   </si>
   <si>
-    <t>9.4</t>
+    <t>8.5</t>
   </si>
   <si>
     <t>Break-Even Year</t>
@@ -726,7 +729,7 @@
     <t>Homeschool Co-Op  |  AZ  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 27, 2026</t>
+    <t>Prepared April 29, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -753,7 +756,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>
@@ -813,7 +816,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -960,7 +963,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>115.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>109.5 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -2111,7 +2114,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B2" s="26">
         <f>'Tuition &amp; Funding Detail'!B14</f>
@@ -2136,7 +2139,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="15">
         <f>'Staffing Plan'!B21</f>
@@ -2161,32 +2164,32 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" s="15">
-        <f>'Operating Expenses'!B11+'Facilities &amp; Occupancy'!B6</f>
-        <v>29625</v>
+        <f>'Operating Expenses'!B12+'Facilities &amp; Occupancy'!B6</f>
+        <v>33375</v>
       </c>
       <c r="C4" s="15">
-        <f>'Operating Expenses'!C11+'Facilities &amp; Occupancy'!C6</f>
-        <v>41211</v>
+        <f>'Operating Expenses'!C12+'Facilities &amp; Occupancy'!C6</f>
+        <v>45823</v>
       </c>
       <c r="D4" s="15">
-        <f>'Operating Expenses'!D11+'Facilities &amp; Occupancy'!D6</f>
-        <v>47815</v>
+        <f>'Operating Expenses'!D12+'Facilities &amp; Occupancy'!D6</f>
+        <v>52543</v>
       </c>
       <c r="E4" s="15">
-        <f>'Operating Expenses'!E11+'Facilities &amp; Occupancy'!E6</f>
-        <v>53325</v>
+        <f>'Operating Expenses'!E12+'Facilities &amp; Occupancy'!E6</f>
+        <v>58171</v>
       </c>
       <c r="F4" s="15">
-        <f>'Operating Expenses'!F11+'Facilities &amp; Occupancy'!F6</f>
-        <v>57646</v>
+        <f>'Operating Expenses'!F12+'Facilities &amp; Occupancy'!F6</f>
+        <v>62613</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B5" s="15">
         <v>0</v>
@@ -2206,110 +2209,110 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B6" s="27">
         <f>SUM(B3:B5)</f>
-        <v>94141</v>
+        <v>97891</v>
       </c>
       <c r="C6" s="27">
         <f>SUM(C3:C5)</f>
-        <v>120953</v>
+        <v>125565</v>
       </c>
       <c r="D6" s="27">
         <f>SUM(D3:D5)</f>
-        <v>129949</v>
+        <v>134677</v>
       </c>
       <c r="E6" s="27">
         <f>SUM(E3:E5)</f>
-        <v>137923</v>
+        <v>142769</v>
       </c>
       <c r="F6" s="27">
         <f>SUM(F3:F5)</f>
-        <v>144782</v>
+        <v>149749</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B7" s="28">
         <f>B2-B6</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C7" s="28">
         <f>C2-C6</f>
-        <v>182027</v>
+        <v>177415</v>
       </c>
       <c r="D7" s="28">
         <f>D2-D6</f>
-        <v>294780</v>
+        <v>290053</v>
       </c>
       <c r="E7" s="28">
         <f>E2-E6</f>
-        <v>385657</v>
+        <v>380811</v>
       </c>
       <c r="F7" s="28">
         <f>F2-F6</f>
-        <v>453458</v>
+        <v>448490</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B8" s="14">
         <f>IF(B2=0,0,B7/B2)</f>
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="C8" s="14">
         <f>IF(C2=0,0,C7/C2)</f>
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="D8" s="14">
         <f>IF(D2=0,0,D7/D2)</f>
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="E8" s="14">
         <f>IF(E2=0,0,E7/E2)</f>
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="F8" s="14">
         <f>IF(F2=0,0,F7/F2)</f>
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B9" s="26">
         <f>B7</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C9" s="26">
         <f>B9+C7</f>
-        <v>255386</v>
+        <v>247024</v>
       </c>
       <c r="D9" s="26">
         <f>C9+D7</f>
-        <v>550166</v>
+        <v>537077</v>
       </c>
       <c r="E9" s="26">
         <f>D9+E7</f>
-        <v>935823</v>
+        <v>917888</v>
       </c>
       <c r="F9" s="26">
         <f>E9+F7</f>
-        <v>1389281</v>
+        <v>1366378</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C10" s="30" t="s">
         <v>1</v>
@@ -2368,7 +2371,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2378,27 +2381,27 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B3" s="15">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C3" s="15">
-        <v>255386</v>
+        <v>247024</v>
       </c>
       <c r="D3" s="15">
-        <v>550166</v>
+        <v>537077</v>
       </c>
       <c r="E3" s="15">
-        <v>935823</v>
+        <v>917888</v>
       </c>
       <c r="F3" s="15">
-        <v>1389281</v>
+        <v>1366378</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B4" s="15">
         <v>0</v>
@@ -2418,32 +2421,32 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B5" s="16">
         <f>SUM(B3:B4)</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C5" s="16">
         <f>SUM(C3:C4)</f>
-        <v>255386</v>
+        <v>247024</v>
       </c>
       <c r="D5" s="16">
         <f>SUM(D3:D4)</f>
-        <v>550166</v>
+        <v>537077</v>
       </c>
       <c r="E5" s="16">
         <f>SUM(E3:E4)</f>
-        <v>935823</v>
+        <v>917888</v>
       </c>
       <c r="F5" s="16">
         <f>SUM(F3:F4)</f>
-        <v>1389281</v>
+        <v>1366378</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -2453,7 +2456,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B8" s="15">
         <v>0</v>
@@ -2473,7 +2476,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B9" s="15">
         <v>0</v>
@@ -2493,7 +2496,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B10" s="16" t="str">
         <f>SUM(B8:B9)</f>
@@ -2518,7 +2521,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2528,72 +2531,72 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B13" s="15">
         <v>0</v>
       </c>
       <c r="C13" s="15">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="D13" s="15">
-        <v>255386</v>
+        <v>247024</v>
       </c>
       <c r="E13" s="15">
-        <v>550166</v>
+        <v>537077</v>
       </c>
       <c r="F13" s="15">
-        <v>935823</v>
+        <v>917888</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" s="15">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C14" s="15">
-        <v>182027</v>
+        <v>177415</v>
       </c>
       <c r="D14" s="15">
-        <v>294780</v>
+        <v>290053</v>
       </c>
       <c r="E14" s="15">
-        <v>385657</v>
+        <v>380811</v>
       </c>
       <c r="F14" s="15">
-        <v>453458</v>
+        <v>448490</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" s="16">
         <f>B5-B10</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C15" s="16">
         <f>C5-C10</f>
-        <v>255386</v>
+        <v>247024</v>
       </c>
       <c r="D15" s="16">
         <f>D5-D10</f>
-        <v>550166</v>
+        <v>537077</v>
       </c>
       <c r="E15" s="16">
         <f>E5-E10</f>
-        <v>935823</v>
+        <v>917888</v>
       </c>
       <c r="F15" s="16">
         <f>F5-F10</f>
-        <v>1389281</v>
+        <v>1366378</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B17" s="26" t="str">
         <f>B5-B10-B15</f>
@@ -2660,7 +2663,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2670,27 +2673,27 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B3" s="15">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C3" s="15">
-        <v>182027</v>
+        <v>177415</v>
       </c>
       <c r="D3" s="15">
-        <v>294781</v>
+        <v>290053</v>
       </c>
       <c r="E3" s="15">
-        <v>385657</v>
+        <v>380811</v>
       </c>
       <c r="F3" s="15">
-        <v>453458</v>
+        <v>448491</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B4" s="15">
         <v>0</v>
@@ -2710,27 +2713,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -2740,92 +2743,92 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B8" s="15">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C8" s="15">
-        <v>255386</v>
+        <v>247024</v>
       </c>
       <c r="D8" s="15">
-        <v>550166</v>
+        <v>537077</v>
       </c>
       <c r="E8" s="15">
-        <v>935823</v>
+        <v>917888</v>
       </c>
       <c r="F8" s="15">
-        <v>1389281</v>
+        <v>1366378</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B9" s="15">
-        <v>7845</v>
+        <v>8158</v>
       </c>
       <c r="C9" s="15">
-        <v>10079</v>
+        <v>10464</v>
       </c>
       <c r="D9" s="15">
-        <v>10829</v>
+        <v>11223</v>
       </c>
       <c r="E9" s="15">
-        <v>11494</v>
+        <v>11897</v>
       </c>
       <c r="F9" s="15">
-        <v>12065</v>
+        <v>12479</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B10" s="32">
         <f>IF(B9=0,0,B8/B9)</f>
-        <v>9.35</v>
+        <v>8.53</v>
       </c>
       <c r="C10" s="32">
         <f>IF(C9=0,0,C8/C9)</f>
-        <v>25.34</v>
+        <v>23.61</v>
       </c>
       <c r="D10" s="32">
         <f>IF(D9=0,0,D8/D9)</f>
-        <v>50.8</v>
+        <v>47.86</v>
       </c>
       <c r="E10" s="32">
         <f>IF(E9=0,0,E8/E9)</f>
-        <v>81.42</v>
+        <v>77.15</v>
       </c>
       <c r="F10" s="32">
         <f>IF(F9=0,0,F8/F9)</f>
-        <v>115.15</v>
+        <v>109.49</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B11" s="33">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="C11" s="33">
-        <v>771</v>
+        <v>718</v>
       </c>
       <c r="D11" s="33">
-        <v>1545</v>
+        <v>1456</v>
       </c>
       <c r="E11" s="33">
-        <v>2477</v>
+        <v>2347</v>
       </c>
       <c r="F11" s="33">
-        <v>3502</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -2835,27 +2838,27 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B15" s="35" t="str">
         <f>IF(B10&gt;=2,"PASS","FAIL")</f>
@@ -2880,42 +2883,42 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="D17" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="B17" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>188</v>
-      </c>
       <c r="E17" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2943,53 +2946,53 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>35</v>
@@ -2997,59 +3000,59 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B16" s="18">
         <v>167500</v>
@@ -3057,31 +3060,31 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B17" s="18">
-        <v>94141</v>
+        <v>97891</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B18" s="18">
-        <v>73359</v>
+        <v>69609</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" s="40">
-        <v>0.4379641791044776</v>
+        <v>0.41557611940298506</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B20" s="18">
         <v>0</v>
@@ -3089,15 +3092,15 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" s="18">
-        <v>73359</v>
+        <v>69609</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" s="18">
         <v>0</v>
@@ -3105,23 +3108,23 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>35</v>
@@ -3129,7 +3132,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B26" s="18">
         <v>11167</v>
@@ -3137,10 +3140,10 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B27" s="18">
-        <v>6276</v>
+        <v>6526</v>
       </c>
     </row>
   </sheetData>
@@ -3181,7 +3184,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B2" s="41"/>
       <c r="C2" s="41"/>
@@ -3191,7 +3194,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
@@ -3201,7 +3204,7 @@
     </row>
     <row r="4" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B4" s="43"/>
       <c r="C4" s="43"/>
@@ -3256,7 +3259,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B8" s="26">
         <f>'5-Year P&amp;L'!B2</f>
@@ -3281,127 +3284,127 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B9" s="15">
         <f>'5-Year P&amp;L'!B6</f>
-        <v>94141</v>
+        <v>97891</v>
       </c>
       <c r="C9" s="15">
         <f>'5-Year P&amp;L'!C6</f>
-        <v>120953</v>
+        <v>125565</v>
       </c>
       <c r="D9" s="15">
         <f>'5-Year P&amp;L'!D6</f>
-        <v>129949</v>
+        <v>134677</v>
       </c>
       <c r="E9" s="15">
         <f>'5-Year P&amp;L'!E6</f>
-        <v>137923</v>
+        <v>142769</v>
       </c>
       <c r="F9" s="15">
         <f>'5-Year P&amp;L'!F6</f>
-        <v>144782</v>
+        <v>149749</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B10" s="23">
         <f>'5-Year P&amp;L'!B7</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C10" s="23">
         <f>'5-Year P&amp;L'!C7</f>
-        <v>182027</v>
+        <v>177415</v>
       </c>
       <c r="D10" s="23">
         <f>'5-Year P&amp;L'!D7</f>
-        <v>294780</v>
+        <v>290053</v>
       </c>
       <c r="E10" s="23">
         <f>'5-Year P&amp;L'!E7</f>
-        <v>385657</v>
+        <v>380811</v>
       </c>
       <c r="F10" s="23">
         <f>'5-Year P&amp;L'!F7</f>
-        <v>453458</v>
+        <v>448490</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B11" s="14">
         <f>IF(B8=0,0,B10/B8)</f>
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="C11" s="14">
         <f>IF(C8=0,0,C10/C8)</f>
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="D11" s="14">
         <f>IF(D8=0,0,D10/D8)</f>
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="E11" s="14">
         <f>IF(E8=0,0,E10/E8)</f>
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="F11" s="14">
         <f>IF(F8=0,0,F10/F8)</f>
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" s="26">
         <f>B10</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C12" s="26">
         <f>B12+C10</f>
-        <v>255386</v>
+        <v>247024</v>
       </c>
       <c r="D12" s="26">
         <f>C12+D10</f>
-        <v>550166</v>
+        <v>537077</v>
       </c>
       <c r="E12" s="26">
         <f>D12+E10</f>
-        <v>935823</v>
+        <v>917888</v>
       </c>
       <c r="F12" s="26">
         <f>E12+F10</f>
-        <v>1389281</v>
+        <v>1366378</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B13" s="26">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C13" s="26">
-        <v>255386</v>
+        <v>247024</v>
       </c>
       <c r="D13" s="26">
-        <v>550166</v>
+        <v>537077</v>
       </c>
       <c r="E13" s="26">
-        <v>935823</v>
+        <v>917888</v>
       </c>
       <c r="F13" s="26">
-        <v>1389281</v>
+        <v>1366378</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B14" s="15">
         <v>11167</v>
@@ -3421,27 +3424,27 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B15" s="15">
-        <v>6276</v>
+        <v>6526</v>
       </c>
       <c r="C15" s="15">
-        <v>5498</v>
+        <v>5708</v>
       </c>
       <c r="D15" s="15">
-        <v>4332</v>
+        <v>4489</v>
       </c>
       <c r="E15" s="15">
-        <v>3831</v>
+        <v>3966</v>
       </c>
       <c r="F15" s="15">
-        <v>3620</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="43" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B17" s="43"/>
       <c r="C17" s="43"/>
@@ -3484,13 +3487,13 @@
     <row r="2" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="44" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C3" s="44"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C4" s="45"/>
     </row>
@@ -3500,7 +3503,7 @@
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
@@ -3511,28 +3514,28 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="49" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C10" s="49"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="47" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C16" s="26">
         <v>598240</v>
@@ -3540,122 +3543,122 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C17" s="26">
-        <v>453458</v>
+        <v>448490</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C18" s="26">
-        <v>1389281</v>
+        <v>1366378</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C22" s="5"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="52" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C23" s="53"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="52" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C24" s="53"/>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="52" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C25" s="53"/>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="52" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C26" s="53"/>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C27" s="53"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C28" s="53"/>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="52" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C29" s="53"/>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="52" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C30" s="53"/>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="52" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C31" s="53"/>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="52" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C32" s="53"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="52" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C33" s="53"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C34" s="53"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C35" s="53"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C36" s="53"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="43" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C39" s="43"/>
     </row>
@@ -3706,7 +3709,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="37" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -3717,7 +3720,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="54" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
@@ -3728,18 +3731,18 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C6" s="58" t="s">
         <v>23</v>
@@ -3757,12 +3760,12 @@
         <v>27</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C7" s="59">
         <v>15</v>
@@ -3782,7 +3785,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C8" s="60">
         <v>167500</v>
@@ -3802,7 +3805,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C9" s="60">
         <v>64516</v>
@@ -3822,27 +3825,27 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C10" s="60">
-        <v>29625</v>
+        <v>33375</v>
       </c>
       <c r="D10" s="60">
-        <v>41211</v>
+        <v>45823</v>
       </c>
       <c r="E10" s="60">
-        <v>47815</v>
+        <v>52543</v>
       </c>
       <c r="F10" s="60">
-        <v>53325</v>
+        <v>58171</v>
       </c>
       <c r="G10" s="60">
-        <v>57646</v>
+        <v>62613</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="60">
         <v>0</v>
@@ -3862,67 +3865,67 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="61" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C12" s="62">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="D12" s="62">
-        <v>182027</v>
+        <v>177415</v>
       </c>
       <c r="E12" s="62">
-        <v>294780</v>
+        <v>290053</v>
       </c>
       <c r="F12" s="62">
-        <v>385657</v>
+        <v>380811</v>
       </c>
       <c r="G12" s="62">
-        <v>453458</v>
+        <v>448490</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="61" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C13" s="62">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="D13" s="62">
-        <v>255386</v>
+        <v>247024</v>
       </c>
       <c r="E13" s="62">
-        <v>550166</v>
+        <v>537077</v>
       </c>
       <c r="F13" s="62">
-        <v>935823</v>
+        <v>917888</v>
       </c>
       <c r="G13" s="62">
-        <v>1389281</v>
+        <v>1366378</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="61" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C14" s="63">
-        <v>0.4379641791044776</v>
+        <v>0.41557611940298506</v>
       </c>
       <c r="D14" s="63">
-        <v>0.600788830945937</v>
+        <v>0.5855667040728761</v>
       </c>
       <c r="E14" s="63">
-        <v>0.6940409201139548</v>
+        <v>0.6829114967155605</v>
       </c>
       <c r="F14" s="63">
-        <v>0.7365770273883647</v>
+        <v>0.7273215172466481</v>
       </c>
       <c r="G14" s="63">
-        <v>0.7579867611660872</v>
+        <v>0.7496824017116877</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="61" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C15" s="64">
         <v>11166.666666666666</v>
@@ -3940,32 +3943,32 @@
         <v>14956</v>
       </c>
       <c r="H15" s="65" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" s="66">
-        <v>6276.066666666667</v>
+        <v>6526.066666666667</v>
       </c>
       <c r="D16" s="66">
-        <v>5497.863636363636</v>
+        <v>5707.5</v>
       </c>
       <c r="E16" s="66">
-        <v>4331.633333333333</v>
+        <v>4489.233333333334</v>
       </c>
       <c r="F16" s="66">
-        <v>3831.1944444444443</v>
+        <v>3965.8055555555557</v>
       </c>
       <c r="G16" s="66">
-        <v>3619.55</v>
+        <v>3743.725</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C17" s="60">
         <v>0</v>
@@ -3985,7 +3988,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C18" s="64">
         <v>1720</v>
@@ -4003,32 +4006,32 @@
         <v>723.675110915625</v>
       </c>
       <c r="H18" s="65" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C19" s="67">
-        <v>4890.6</v>
+        <v>4640.6</v>
       </c>
       <c r="D19" s="67">
-        <v>8273.954545454546</v>
+        <v>8064.318181818182</v>
       </c>
       <c r="E19" s="67">
-        <v>9826</v>
+        <v>9668.433333333332</v>
       </c>
       <c r="F19" s="67">
-        <v>10712.694444444445</v>
+        <v>10578.083333333334</v>
       </c>
       <c r="G19" s="67">
-        <v>11336.45</v>
+        <v>11212.25</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="61" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C20" s="63">
         <v>0.38517014925373133</v>
@@ -4046,12 +4049,12 @@
         <v>0.1456539181599358</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="61" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C21" s="68">
         <v>0.15402985074626865</v>
@@ -4069,35 +4072,35 @@
         <v>0.04838694242548977</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="61" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C22" s="63">
-        <v>0.4379641791044776</v>
+        <v>0.41557611940298506</v>
       </c>
       <c r="D22" s="63">
-        <v>0.600788830945937</v>
+        <v>0.5855667040728761</v>
       </c>
       <c r="E22" s="63">
-        <v>0.6940432745508912</v>
+        <v>0.6829114967155605</v>
       </c>
       <c r="F22" s="63">
-        <v>0.7365770273883647</v>
+        <v>0.7273215172466481</v>
       </c>
       <c r="G22" s="63">
-        <v>0.7579867611660872</v>
+        <v>0.7496840732816261</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="61" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C23" s="69">
         <v>3</v>
@@ -4115,35 +4118,35 @@
         <v>3</v>
       </c>
       <c r="H23" s="65" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="61" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C24" s="70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D24" s="70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E24" s="70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F24" s="70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G24" s="70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H24" s="65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="61" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C25" s="29" t="str">
         <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
@@ -4171,175 +4174,175 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="61" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C26" s="72">
         <v>9</v>
       </c>
       <c r="D26" s="69">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26" s="69">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F26" s="73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G26" s="73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H26" s="65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="61" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="69">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="D27" s="69">
-        <v>771</v>
+        <v>718</v>
       </c>
       <c r="E27" s="69">
-        <v>1545</v>
+        <v>1456</v>
       </c>
       <c r="F27" s="69">
-        <v>2477</v>
+        <v>2347</v>
       </c>
       <c r="G27" s="69">
-        <v>3502</v>
+        <v>3330</v>
       </c>
       <c r="H27" s="65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="74" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D30" s="75" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E30" s="75"/>
       <c r="F30" s="76" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G30" s="76"/>
       <c r="H30" s="76"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="74" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D31" s="75" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E31" s="75"/>
       <c r="F31" s="76" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G31" s="76"/>
       <c r="H31" s="76"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="74" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D32" s="75" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E32" s="75"/>
       <c r="F32" s="76" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G32" s="76"/>
       <c r="H32" s="76"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="74" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E33" s="75"/>
       <c r="F33" s="76" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G33" s="76"/>
       <c r="H33" s="76"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="74" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D34" s="75" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E34" s="75"/>
       <c r="F34" s="76" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G34" s="76"/>
       <c r="H34" s="76"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="74" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D35" s="75" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E35" s="75"/>
       <c r="F35" s="76" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G35" s="76"/>
       <c r="H35" s="76"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="74" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C37" s="61" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D37" s="61"/>
       <c r="E37" s="61"/>
@@ -4347,7 +4350,7 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="77" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C39" s="77"/>
       <c r="D39" s="77"/>
@@ -5310,7 +5313,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -5467,49 +5470,74 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="16">
-        <v>0</v>
-      </c>
-      <c r="C9" s="16">
-        <v>0</v>
-      </c>
-      <c r="D9" s="16">
-        <v>0</v>
-      </c>
-      <c r="E9" s="16">
-        <v>0</v>
-      </c>
-      <c r="F9" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="B9" s="15">
+        <v>4500</v>
+      </c>
+      <c r="C9" s="15">
+        <v>4613</v>
+      </c>
+      <c r="D9" s="15">
+        <v>4728</v>
+      </c>
+      <c r="E9" s="15">
+        <v>4846</v>
+      </c>
+      <c r="F9" s="15">
+        <v>4967</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="16">
-        <f>B4+B7+B9</f>
-        <v>9750</v>
-      </c>
-      <c r="C11" s="16">
-        <f>C4+C7+C9</f>
-        <v>14658</v>
-      </c>
-      <c r="D11" s="16">
-        <f>D4+D7+D9</f>
-        <v>20487</v>
-      </c>
-      <c r="E11" s="16">
-        <f>E4+E7+E9</f>
-        <v>25199</v>
-      </c>
-      <c r="F11" s="16">
-        <f>F4+F7+F9</f>
-        <v>28699</v>
+      <c r="B10" s="16">
+        <f>SUM(B9:B9)</f>
+        <v>4500</v>
+      </c>
+      <c r="C10" s="16">
+        <f>SUM(C9:C9)</f>
+        <v>4613</v>
+      </c>
+      <c r="D10" s="16">
+        <f>SUM(D9:D9)</f>
+        <v>4728</v>
+      </c>
+      <c r="E10" s="16">
+        <f>SUM(E9:E9)</f>
+        <v>4846</v>
+      </c>
+      <c r="F10" s="16">
+        <f>SUM(F9:F9)</f>
+        <v>4967</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="16">
+        <f>B4+B7+B10</f>
+        <v>14250</v>
+      </c>
+      <c r="C12" s="16">
+        <f>C4+C7+C10</f>
+        <v>19271</v>
+      </c>
+      <c r="D12" s="16">
+        <f>D4+D7+D10</f>
+        <v>25215</v>
+      </c>
+      <c r="E12" s="16">
+        <f>E4+E7+E10</f>
+        <v>30045</v>
+      </c>
+      <c r="F12" s="16">
+        <f>F4+F7+F10</f>
+        <v>33666</v>
       </c>
     </row>
   </sheetData>
@@ -5556,7 +5584,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5566,7 +5594,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" s="15">
         <v>21600</v>
@@ -5586,7 +5614,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" s="15">
         <v>2400</v>
@@ -5606,7 +5634,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" s="15">
         <v>1800</v>
@@ -5626,7 +5654,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" s="16">
         <f>SUM(B3:B5)</f>
@@ -5651,7 +5679,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" s="15">
         <v>1720</v>
@@ -5671,7 +5699,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B9" s="14">
         <v>0.15402985074626865</v>
@@ -5713,19 +5741,19 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B4" s="22">
         <v>0</v>
@@ -5733,7 +5761,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B5" s="23" t="str">
         <f>SUM(B4:B4)</f>
@@ -5742,13 +5770,13 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B7" s="5"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B8" s="22">
         <v>4300</v>
@@ -5756,7 +5784,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B9" s="22">
         <v>1875</v>
@@ -5764,7 +5792,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10" s="22">
         <v>6000</v>
@@ -5772,41 +5800,41 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B11" s="22">
-        <v>15690</v>
+        <v>16315</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" s="22">
-        <v>1393</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" s="23">
         <f>SUM(B8:B12)</f>
-        <v>29258</v>
+        <v>29915</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="24">
         <f>B5-B13</f>
-        <v>-29258</v>
+        <v>-29915</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -5838,7 +5866,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5849,35 +5877,35 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -5888,7 +5916,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B7" s="18">
         <v>0</v>
@@ -5896,7 +5924,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B8" s="19">
         <v>0</v>
@@ -5904,7 +5932,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -5947,45 +5975,45 @@
         <v>18</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B2" s="15">
         <v>103800</v>
@@ -6030,7 +6058,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="15">
         <v>6452</v>
@@ -6075,37 +6103,37 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" s="15">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="C4" s="15">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="D4" s="15">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="E4" s="15">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="F4" s="15">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="G4" s="15">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="H4" s="15">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="I4" s="15">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="J4" s="15">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="K4" s="15">
-        <v>2958</v>
+        <v>3333</v>
       </c>
       <c r="L4" s="15">
         <v>0</v>
@@ -6115,12 +6143,12 @@
       </c>
       <c r="N4" s="15">
         <f>SUM(B4:M4)</f>
-        <v>29625</v>
+        <v>33375</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="15">
         <v>0</v>
@@ -6165,47 +6193,47 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B6" s="23">
         <f>SUM(B3:B5)</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="C6" s="23">
         <f>SUM(C3:C5)</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="D6" s="23">
         <f>SUM(D3:D5)</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="E6" s="23">
         <f>SUM(E3:E5)</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="F6" s="23">
         <f>SUM(F3:F5)</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="G6" s="23">
         <f>SUM(G3:G5)</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="H6" s="23">
         <f>SUM(H3:H5)</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="I6" s="23">
         <f>SUM(I3:I5)</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="J6" s="23">
         <f>SUM(J3:J5)</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="K6" s="23">
         <f>SUM(K3:K5)</f>
-        <v>9406</v>
+        <v>9781</v>
       </c>
       <c r="L6" s="23" t="str">
         <f>SUM(L3:L5)</f>
@@ -6217,52 +6245,52 @@
       </c>
       <c r="N6" s="23">
         <f>SUM(B6:M6)</f>
-        <v>94141</v>
+        <v>97891</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B7" s="26">
         <f>B2-B6</f>
-        <v>94385</v>
+        <v>94010</v>
       </c>
       <c r="C7" s="26">
         <f>C2-C6</f>
-        <v>1385</v>
+        <v>1010</v>
       </c>
       <c r="D7" s="26">
         <f>D2-D6</f>
-        <v>1385</v>
+        <v>1010</v>
       </c>
       <c r="E7" s="26">
         <f>E2-E6</f>
-        <v>1385</v>
+        <v>1010</v>
       </c>
       <c r="F7" s="26">
         <f>F2-F6</f>
-        <v>1385</v>
+        <v>1010</v>
       </c>
       <c r="G7" s="26">
         <f>G2-G6</f>
-        <v>1385</v>
+        <v>1010</v>
       </c>
       <c r="H7" s="26">
         <f>H2-H6</f>
-        <v>1385</v>
+        <v>1010</v>
       </c>
       <c r="I7" s="26">
         <f>I2-I6</f>
-        <v>1385</v>
+        <v>1010</v>
       </c>
       <c r="J7" s="26">
         <f>J2-J6</f>
-        <v>1385</v>
+        <v>1010</v>
       </c>
       <c r="K7" s="26">
         <f>K2-K6</f>
-        <v>-32106</v>
+        <v>-32481</v>
       </c>
       <c r="L7" s="26" t="str">
         <f>L2-L6</f>
@@ -6274,69 +6302,69 @@
       </c>
       <c r="N7" s="26">
         <f>SUM(B7:M7)</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B8" s="26">
         <f>0+B7</f>
-        <v>94385</v>
+        <v>94010</v>
       </c>
       <c r="C8" s="26">
         <f>B8+C7</f>
-        <v>95770</v>
+        <v>95020</v>
       </c>
       <c r="D8" s="26">
         <f>C8+D7</f>
-        <v>97155</v>
+        <v>96030</v>
       </c>
       <c r="E8" s="26">
         <f>D8+E7</f>
-        <v>98540</v>
+        <v>97040</v>
       </c>
       <c r="F8" s="26">
         <f>E8+F7</f>
-        <v>99925</v>
+        <v>98050</v>
       </c>
       <c r="G8" s="26">
         <f>F8+G7</f>
-        <v>101310</v>
+        <v>99060</v>
       </c>
       <c r="H8" s="26">
         <f>G8+H7</f>
-        <v>102695</v>
+        <v>100070</v>
       </c>
       <c r="I8" s="26">
         <f>H8+I7</f>
-        <v>104080</v>
+        <v>101080</v>
       </c>
       <c r="J8" s="26">
         <f>I8+J7</f>
-        <v>105465</v>
+        <v>102090</v>
       </c>
       <c r="K8" s="26">
         <f>J8+K7</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="L8" s="26">
         <f>K8+L7</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="M8" s="26">
         <f>L8+M7</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="N8" s="26">
         <f>M8</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -6354,7 +6382,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B11" s="19">
         <v>0</v>
@@ -6362,20 +6390,20 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" s="18">
         <f>M8</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B13" s="19">
         <f>MIN(B8:M8)</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
     </row>
   </sheetData>
